--- a/docs/project/NEMO_Tracking.xlsx
+++ b/docs/project/NEMO_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://technionmail.sharepoint.com/sites/NEMOProject/Shared Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rahafaburaya/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DF793A-CEF4-1A4F-A35A-AB28CC232244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B64EAF1-26EB-A341-90D1-7969267650A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41380" yWindow="1380" windowWidth="36520" windowHeight="23620" activeTab="15" xr2:uid="{AF7D7499-D775-1A4F-A8DC-0237DA4F4B06}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="14580" firstSheet="7" activeTab="16" xr2:uid="{AF7D7499-D775-1A4F-A8DC-0237DA4F4B06}"/>
   </bookViews>
   <sheets>
     <sheet name="Chips List" sheetId="1" r:id="rId1"/>
@@ -3086,6 +3086,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3098,6 +3101,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3106,12 +3112,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3122,20 +3122,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3147,6 +3141,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3155,23 +3167,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3884,21 +3884,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EA72C4-4A3D-004D-A7F5-BE6201CD3D5C}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="19.48046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="136" t="s">
+    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3915,396 +3915,395 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="135">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="128">
         <v>1</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="128" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="128" t="s">
+      <c r="D3" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="E3" s="130" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="135"/>
-      <c r="B4" s="135"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="128"/>
+      <c r="B4" s="128"/>
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="128"/>
-      <c r="E4" s="130"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="135"/>
-      <c r="B5" s="135"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="131"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="128"/>
+      <c r="B5" s="128"/>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="128"/>
-      <c r="E5" s="130"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="135"/>
-      <c r="B6" s="135"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="131"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="128"/>
+      <c r="B6" s="128"/>
       <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="128"/>
-      <c r="E6" s="130"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="135"/>
-      <c r="B7" s="135"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="131"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="128"/>
+      <c r="B7" s="128"/>
       <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="131"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="135">
+      <c r="D7" s="129"/>
+      <c r="E7" s="132"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="128">
         <v>2</v>
       </c>
-      <c r="B8" s="135" t="s">
+      <c r="B8" s="128" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="128" t="s">
+      <c r="D8" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="129" t="s">
+      <c r="E8" s="130" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="135"/>
-      <c r="B9" s="135"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="128"/>
+      <c r="B9" s="128"/>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="128"/>
-      <c r="E9" s="130"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="135"/>
-      <c r="B10" s="135"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="131"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="128"/>
+      <c r="B10" s="128"/>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="130"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="135"/>
-      <c r="B11" s="135"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="131"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="128"/>
+      <c r="B11" s="128"/>
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="128"/>
-      <c r="E11" s="131"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="135">
+      <c r="D11" s="129"/>
+      <c r="E11" s="132"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="128">
         <v>3</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="134" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="128" t="s">
+      <c r="D12" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="129" t="s">
+      <c r="E12" s="130" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="135"/>
-      <c r="B13" s="133"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="128"/>
+      <c r="B13" s="135"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="130"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="135"/>
-      <c r="B14" s="133"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="131"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="128"/>
+      <c r="B14" s="135"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="130"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="135"/>
-      <c r="B15" s="134"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="131"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="128"/>
+      <c r="B15" s="136"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="131"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="135">
+      <c r="D15" s="129"/>
+      <c r="E15" s="132"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="128">
         <v>4</v>
       </c>
-      <c r="B16" s="135" t="s">
+      <c r="B16" s="128" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="128" t="s">
+      <c r="D16" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="129" t="s">
+      <c r="E16" s="130" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="135"/>
-      <c r="B17" s="135"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="128"/>
+      <c r="B17" s="128"/>
       <c r="C17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="128"/>
-      <c r="E17" s="130"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="135"/>
-      <c r="B18" s="135"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="131"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="128"/>
+      <c r="B18" s="128"/>
       <c r="C18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="128"/>
-      <c r="E18" s="130"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="135"/>
-      <c r="B19" s="135"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="131"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="128"/>
+      <c r="B19" s="128"/>
       <c r="C19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="128"/>
-      <c r="E19" s="130"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="135"/>
-      <c r="B20" s="135"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="131"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="128"/>
+      <c r="B20" s="128"/>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="128"/>
-      <c r="E20" s="130"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="135"/>
-      <c r="B21" s="135"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="131"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="128"/>
+      <c r="B21" s="128"/>
       <c r="C21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="128"/>
-      <c r="E21" s="131"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="135">
+      <c r="D21" s="129"/>
+      <c r="E21" s="132"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="128">
         <v>5</v>
       </c>
-      <c r="B22" s="135" t="s">
+      <c r="B22" s="128" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="128" t="s">
+      <c r="D22" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="129" t="s">
+      <c r="E22" s="130" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="135"/>
-      <c r="B23" s="135"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="128"/>
+      <c r="B23" s="128"/>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="128"/>
-      <c r="E23" s="130"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="135"/>
-      <c r="B24" s="135"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="131"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="128"/>
+      <c r="B24" s="128"/>
       <c r="C24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="130"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="135"/>
-      <c r="B25" s="135"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="131"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="128"/>
+      <c r="B25" s="128"/>
       <c r="C25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="128"/>
-      <c r="E25" s="130"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="135"/>
-      <c r="B26" s="135"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="131"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="128"/>
+      <c r="B26" s="128"/>
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="128"/>
-      <c r="E26" s="130"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="135"/>
-      <c r="B27" s="135"/>
+      <c r="D26" s="129"/>
+      <c r="E26" s="131"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="128"/>
+      <c r="B27" s="128"/>
       <c r="C27" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="128"/>
-      <c r="E27" s="131"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="135">
+      <c r="D27" s="129"/>
+      <c r="E27" s="132"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="128">
         <v>6</v>
       </c>
-      <c r="B28" s="135" t="s">
+      <c r="B28" s="128" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="128" t="s">
+      <c r="D28" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="129" t="s">
+      <c r="E28" s="130" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="135"/>
-      <c r="B29" s="135"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="128"/>
+      <c r="B29" s="128"/>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="128"/>
-      <c r="E29" s="130"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="135"/>
-      <c r="B30" s="135"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="131"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="128"/>
+      <c r="B30" s="128"/>
       <c r="C30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="128"/>
-      <c r="E30" s="130"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="135"/>
-      <c r="B31" s="135"/>
+      <c r="D30" s="129"/>
+      <c r="E30" s="131"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="128"/>
+      <c r="B31" s="128"/>
       <c r="C31" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="128"/>
-      <c r="E31" s="130"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="135"/>
-      <c r="B32" s="135"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="131"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="128"/>
+      <c r="B32" s="128"/>
       <c r="C32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="128"/>
-      <c r="E32" s="130"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="135"/>
-      <c r="B33" s="135"/>
+      <c r="D32" s="129"/>
+      <c r="E32" s="131"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="128"/>
+      <c r="B33" s="128"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="131"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="135">
+      <c r="D33" s="129"/>
+      <c r="E33" s="132"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="128">
         <v>7</v>
       </c>
-      <c r="B34" s="135" t="s">
+      <c r="B34" s="128" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="128" t="s">
+      <c r="D34" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="129" t="s">
+      <c r="E34" s="130" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="135"/>
-      <c r="B35" s="135"/>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="128"/>
+      <c r="B35" s="128"/>
       <c r="C35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="128"/>
-      <c r="E35" s="130"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="135"/>
-      <c r="B36" s="135"/>
+      <c r="D35" s="129"/>
+      <c r="E35" s="131"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="128"/>
+      <c r="B36" s="128"/>
       <c r="C36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="128"/>
-      <c r="E36" s="130"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="135"/>
-      <c r="B37" s="135"/>
+      <c r="D36" s="129"/>
+      <c r="E36" s="131"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="128"/>
+      <c r="B37" s="128"/>
       <c r="C37" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="128"/>
-      <c r="E37" s="130"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="135"/>
-      <c r="B38" s="135"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="131"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="128"/>
+      <c r="B38" s="128"/>
       <c r="C38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="128"/>
-      <c r="E38" s="130"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="135"/>
-      <c r="B39" s="135"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="131"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="128"/>
+      <c r="B39" s="128"/>
       <c r="C39" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="128"/>
-      <c r="E39" s="131"/>
+      <c r="D39" s="129"/>
+      <c r="E39" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
     <mergeCell ref="A34:A39"/>
     <mergeCell ref="B34:B39"/>
     <mergeCell ref="D34:D39"/>
@@ -4317,14 +4316,15 @@
     <mergeCell ref="B22:B27"/>
     <mergeCell ref="D22:D27"/>
     <mergeCell ref="E22:E27"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4333,15 +4333,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2621D478-D9ED-410A-BF1C-53B46722AE12}">
   <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.94921875" customWidth="1"/>
-    <col min="2" max="2" width="17.5078125" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="11.9609375" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>285</v>
       </c>
@@ -4355,62 +4355,62 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="40" t="s">
         <v>214</v>
       </c>
@@ -4418,37 +4418,37 @@
         <v>309</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="40" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="40" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F19" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>316</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>319</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>321</v>
       </c>
@@ -4481,17 +4481,17 @@
         <v>322</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F23" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>325</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -4510,12 +4510,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>328</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>330</v>
       </c>
@@ -4537,12 +4537,12 @@
         <v>331</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>333</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>334</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>336</v>
       </c>
@@ -4575,12 +4575,12 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>339</v>
       </c>
@@ -4591,12 +4591,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>342</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G43" s="16" t="s">
         <v>344</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="16" t="s">
         <v>15</v>
       </c>
@@ -4635,32 +4635,32 @@
         <v>350</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="16" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>336</v>
       </c>
@@ -4673,20 +4673,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1C2D4E-05E3-48A4-BCE9-D2E10BA5AF56}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.52734375" customWidth="1"/>
-    <col min="2" max="2" width="18.98828125" customWidth="1"/>
-    <col min="3" max="3" width="68.4375" customWidth="1"/>
-    <col min="4" max="4" width="29.46875" customWidth="1"/>
-    <col min="5" max="5" width="22.8125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="68.5" customWidth="1"/>
+    <col min="4" max="4" width="29.5" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="29.34765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9453125" customWidth="1"/>
-    <col min="9" max="9" width="22.93359375" customWidth="1"/>
+    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="63" t="s">
         <v>223</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A2" s="58" t="s">
         <v>333</v>
       </c>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="J2" s="58"/>
     </row>
-    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>336</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A5" s="61" t="s">
         <v>368</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A6" s="61" t="s">
         <v>371</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A7" s="61" t="s">
         <v>353</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>325</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>326</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A10" s="58" t="s">
         <v>380</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>383</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>214</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>388</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="58" t="s">
         <v>391</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
       <c r="F16" s="58"/>
@@ -5083,16 +5083,16 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9111904-421A-2B44-9E5C-3BD64A13048C}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5234375" style="5" customWidth="1"/>
-    <col min="2" max="3" width="7.02734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5234375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.9453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5234375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="25.5" style="5" customWidth="1"/>
+    <col min="2" max="3" width="7" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>393</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>399</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="88.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>402</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>405</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="59.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>407</v>
       </c>
@@ -5190,117 +5190,117 @@
         <v>409</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="153" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="140" t="s">
         <v>410</v>
       </c>
-      <c r="B6" s="145">
+      <c r="B6" s="143">
         <v>45717</v>
       </c>
-      <c r="C6" s="145">
+      <c r="C6" s="143">
         <v>45809</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="151" t="s">
+      <c r="E6" s="146" t="s">
         <v>411</v>
       </c>
-      <c r="F6" s="153" t="s">
+      <c r="F6" s="140" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="155"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="141"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
       <c r="D7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="156"/>
-      <c r="F7" s="155"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="154"/>
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="141"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="142"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
       <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="152"/>
-      <c r="F8" s="154"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="153" t="s">
+      <c r="E8" s="148"/>
+      <c r="F8" s="142"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="140" t="s">
         <v>413</v>
       </c>
-      <c r="B9" s="145">
+      <c r="B9" s="143">
         <v>45717</v>
       </c>
-      <c r="C9" s="145">
+      <c r="C9" s="143">
         <v>45992</v>
       </c>
-      <c r="D9" s="151" t="s">
+      <c r="D9" s="146" t="s">
         <v>72</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="F9" s="153" t="s">
+      <c r="F9" s="140" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
-      <c r="B10" s="146"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="156"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="141"/>
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="147"/>
       <c r="E10" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="F10" s="155"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="154"/>
-      <c r="B11" s="147"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="152"/>
+      <c r="F10" s="141"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="142"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="148"/>
       <c r="E11" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="F11" s="154"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="153" t="s">
+      <c r="F11" s="142"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="140" t="s">
         <v>418</v>
       </c>
-      <c r="B12" s="145">
+      <c r="B12" s="143">
         <v>45717</v>
       </c>
-      <c r="C12" s="145">
+      <c r="C12" s="143">
         <v>45992</v>
       </c>
-      <c r="D12" s="151" t="s">
+      <c r="D12" s="146" t="s">
         <v>419</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="F12" s="153" t="s">
+      <c r="F12" s="140" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="154"/>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="152"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="142"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="148"/>
       <c r="E13" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="F13" s="154"/>
-    </row>
-    <row r="14" spans="1:6" ht="59.25" x14ac:dyDescent="0.25">
+      <c r="F13" s="142"/>
+    </row>
+    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>422</v>
       </c>
@@ -5320,35 +5320,35 @@
         <v>423</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="153" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="140" t="s">
         <v>424</v>
       </c>
-      <c r="B15" s="145">
+      <c r="B15" s="143">
         <v>45992</v>
       </c>
-      <c r="C15" s="145">
+      <c r="C15" s="143">
         <v>46174</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="153" t="s">
+      <c r="E15" s="146"/>
+      <c r="F15" s="140" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
-      <c r="B16" s="147"/>
-      <c r="C16" s="147"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="142"/>
+      <c r="B16" s="145"/>
+      <c r="C16" s="145"/>
       <c r="D16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="152"/>
-      <c r="F16" s="154"/>
-    </row>
-    <row r="17" spans="1:6" ht="74.25" x14ac:dyDescent="0.25">
+      <c r="E16" s="148"/>
+      <c r="F16" s="142"/>
+    </row>
+    <row r="17" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>426</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>427</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>430</v>
       </c>
@@ -5404,65 +5404,65 @@
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="142" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="149" t="s">
         <v>433</v>
       </c>
-      <c r="B20" s="145">
+      <c r="B20" s="143">
         <v>46082</v>
       </c>
-      <c r="C20" s="145">
+      <c r="C20" s="143">
         <v>46174</v>
       </c>
-      <c r="D20" s="151" t="s">
+      <c r="D20" s="146" t="s">
         <v>434</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="F20" s="153"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="144"/>
-      <c r="B21" s="147"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="152"/>
+      <c r="F20" s="140"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="150"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="148"/>
       <c r="E21" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="F21" s="154"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="153" t="s">
+      <c r="F21" s="142"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="140" t="s">
         <v>435</v>
       </c>
-      <c r="B22" s="145">
+      <c r="B22" s="143">
         <v>46082</v>
       </c>
-      <c r="C22" s="145">
+      <c r="C22" s="143">
         <v>46266</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="151" t="s">
+      <c r="E22" s="146" t="s">
         <v>436</v>
       </c>
-      <c r="F22" s="153" t="s">
+      <c r="F22" s="140" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="154"/>
-      <c r="B23" s="147"/>
-      <c r="C23" s="147"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="142"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
       <c r="D23" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="152"/>
-      <c r="F23" s="154"/>
-    </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="E23" s="148"/>
+      <c r="F23" s="142"/>
+    </row>
+    <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>438</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="59.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>439</v>
       </c>
@@ -5502,54 +5502,54 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="142" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="149" t="s">
         <v>441</v>
       </c>
-      <c r="B26" s="145">
+      <c r="B26" s="143">
         <v>46266</v>
       </c>
-      <c r="C26" s="145">
+      <c r="C26" s="143">
         <v>46388</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="148" t="s">
+      <c r="E26" s="152" t="s">
         <v>442</v>
       </c>
-      <c r="F26" s="142" t="s">
+      <c r="F26" s="149" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="143"/>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="151"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
       <c r="D27" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="149"/>
-      <c r="F27" s="143"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="144"/>
-      <c r="B28" s="147"/>
-      <c r="C28" s="147"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="151"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="150"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="145"/>
       <c r="D28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="150"/>
-      <c r="F28" s="144"/>
-    </row>
-    <row r="29" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="142" t="s">
+      <c r="E28" s="154"/>
+      <c r="F28" s="150"/>
+    </row>
+    <row r="29" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="149" t="s">
         <v>444</v>
       </c>
-      <c r="B29" s="145">
+      <c r="B29" s="143">
         <v>46447</v>
       </c>
-      <c r="C29" s="145">
+      <c r="C29" s="143">
         <v>46539</v>
       </c>
       <c r="D29" s="9" t="s">
@@ -5560,34 +5560,34 @@
         <v>445</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="143"/>
-      <c r="B30" s="146"/>
-      <c r="C30" s="146"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="151"/>
+      <c r="B30" s="144"/>
+      <c r="C30" s="144"/>
       <c r="D30" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="144"/>
-      <c r="B31" s="147"/>
-      <c r="C31" s="147"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="150"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
       <c r="D31" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="142" t="s">
+    <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" s="149" t="s">
         <v>446</v>
       </c>
-      <c r="B32" s="145">
+      <c r="B32" s="143">
         <v>46508</v>
       </c>
-      <c r="C32" s="145">
+      <c r="C32" s="143">
         <v>46569</v>
       </c>
       <c r="D32" s="9" t="s">
@@ -5600,34 +5600,34 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="143"/>
-      <c r="B33" s="146"/>
-      <c r="C33" s="146"/>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="151"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="144"/>
       <c r="D33" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="144"/>
-      <c r="B34" s="147"/>
-      <c r="C34" s="147"/>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="150"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="145"/>
       <c r="D34" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="142" t="s">
+    <row r="35" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="149" t="s">
         <v>447</v>
       </c>
-      <c r="B35" s="145">
+      <c r="B35" s="143">
         <v>46569</v>
       </c>
-      <c r="C35" s="145">
+      <c r="C35" s="143">
         <v>46600</v>
       </c>
       <c r="D35" s="9" t="s">
@@ -5640,98 +5640,97 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="143"/>
-      <c r="B36" s="146"/>
-      <c r="C36" s="146"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="151"/>
+      <c r="B36" s="144"/>
+      <c r="C36" s="144"/>
       <c r="D36" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="144"/>
-      <c r="B37" s="147"/>
-      <c r="C37" s="147"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="150"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="145"/>
       <c r="D37" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="141" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="156" t="s">
         <v>450</v>
       </c>
-      <c r="B38" s="141"/>
-      <c r="C38" s="141"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="141"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="141" t="s">
+      <c r="B38" s="156"/>
+      <c r="C38" s="156"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
+      <c r="F38" s="156"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="156" t="s">
         <v>451</v>
       </c>
-      <c r="B39" s="141"/>
-      <c r="C39" s="141"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="140" t="s">
+      <c r="B39" s="156"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="156"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="155" t="s">
         <v>452</v>
       </c>
-      <c r="B40" s="140"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="141" t="s">
+      <c r="B40" s="155"/>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="156" t="s">
         <v>453</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="141"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="141"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="141" t="s">
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="156" t="s">
         <v>454</v>
       </c>
-      <c r="B42" s="141"/>
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="156"/>
+      <c r="D42" s="156"/>
+      <c r="E42" s="156"/>
+      <c r="F42" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F26:F28"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="A22:A23"/>
@@ -5742,25 +5741,26 @@
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F9:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5769,12 +5769,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD63F5F-D125-3D46-BB8F-497AD473CB3A}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.9453125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>455</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>461</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>467</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>473</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>478</v>
       </c>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>483</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>487</v>
       </c>
@@ -5902,7 +5902,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>491</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>495</v>
       </c>
@@ -5938,17 +5938,17 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B016E7-BB0B-7840-9BA2-F1D876E7B95D}">
   <dimension ref="A1:N70"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="19.9765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.49609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.00390625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5078125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.9609375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>497</v>
       </c>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="J1" s="46"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>1</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>2</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>3</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>4</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>5</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="M6" s="157"/>
       <c r="N6" s="157"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>6</v>
       </c>
@@ -6162,7 +6162,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>7</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>8</v>
       </c>
@@ -6230,7 +6230,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>9</v>
       </c>
@@ -6264,7 +6264,7 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>10</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>11</v>
       </c>
@@ -6326,7 +6326,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>12</v>
       </c>
@@ -6354,7 +6354,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>13</v>
       </c>
@@ -6382,7 +6382,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>14</v>
       </c>
@@ -6410,7 +6410,7 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>15</v>
       </c>
@@ -6438,7 +6438,7 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>16</v>
       </c>
@@ -6466,7 +6466,7 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>17</v>
       </c>
@@ -6492,7 +6492,7 @@
       <c r="I18" s="42"/>
       <c r="J18" s="42"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>18</v>
       </c>
@@ -6518,7 +6518,7 @@
       <c r="I19" s="42"/>
       <c r="J19" s="42"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>19</v>
       </c>
@@ -6544,7 +6544,7 @@
       <c r="I20" s="42"/>
       <c r="J20" s="42"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>20</v>
       </c>
@@ -6570,7 +6570,7 @@
       <c r="I21" s="42"/>
       <c r="J21" s="42"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>21</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="44" t="s">
         <v>497</v>
       </c>
@@ -6663,7 +6663,7 @@
       <c r="K24" s="50"/>
       <c r="M24" s="51"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>23</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>24</v>
       </c>
@@ -6726,7 +6726,7 @@
       <c r="L26" s="53"/>
       <c r="M26" s="54"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>25</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="I27" s="43"/>
       <c r="J27" s="43"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>26</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>27</v>
       </c>
@@ -6813,7 +6813,7 @@
       <c r="I29" s="43"/>
       <c r="J29" s="43"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>28</v>
       </c>
@@ -6841,7 +6841,7 @@
       <c r="I30" s="43"/>
       <c r="J30" s="43"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>29</v>
       </c>
@@ -6869,7 +6869,7 @@
       <c r="I31" s="43"/>
       <c r="J31" s="43"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>30</v>
       </c>
@@ -6897,7 +6897,7 @@
       <c r="I32" s="43"/>
       <c r="J32" s="43"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>31</v>
       </c>
@@ -6925,7 +6925,7 @@
       <c r="I33" s="43"/>
       <c r="J33" s="43"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>32</v>
       </c>
@@ -6953,7 +6953,7 @@
       <c r="I34" s="43"/>
       <c r="J34" s="43"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>33</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="I35" s="43"/>
       <c r="J35" s="43"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>34</v>
       </c>
@@ -7009,7 +7009,7 @@
       <c r="I36" s="43"/>
       <c r="J36" s="43"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>35</v>
       </c>
@@ -7037,7 +7037,7 @@
       <c r="I37" s="43"/>
       <c r="J37" s="43"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>36</v>
       </c>
@@ -7065,7 +7065,7 @@
       <c r="I38" s="43"/>
       <c r="J38" s="43"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="45">
         <v>37</v>
       </c>
@@ -7093,7 +7093,7 @@
       <c r="I39" s="43"/>
       <c r="J39" s="43"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="45">
         <v>38</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="I40" s="43"/>
       <c r="J40" s="43"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="45">
         <v>39</v>
       </c>
@@ -7149,7 +7149,7 @@
       <c r="I41" s="43"/>
       <c r="J41" s="43"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="45">
         <v>40</v>
       </c>
@@ -7177,7 +7177,7 @@
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="45">
         <v>41</v>
       </c>
@@ -7201,7 +7201,7 @@
       <c r="I43" s="43"/>
       <c r="J43" s="43"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="45">
         <v>42</v>
       </c>
@@ -7225,7 +7225,7 @@
       <c r="I44" s="43"/>
       <c r="J44" s="43"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="45">
         <v>43</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="I45" s="43"/>
       <c r="J45" s="43"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="45">
         <v>44</v>
       </c>
@@ -7273,7 +7273,7 @@
       <c r="I46" s="43"/>
       <c r="J46" s="43"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="45">
         <v>45</v>
       </c>
@@ -7297,7 +7297,7 @@
       <c r="I47" s="43"/>
       <c r="J47" s="43"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="45">
         <v>46</v>
       </c>
@@ -7321,7 +7321,7 @@
       <c r="I48" s="43"/>
       <c r="J48" s="43"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="45">
         <v>47</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="I49" s="43"/>
       <c r="J49" s="43"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="45">
         <v>48</v>
       </c>
@@ -7369,7 +7369,7 @@
       <c r="I50" s="43"/>
       <c r="J50" s="43"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="45">
         <v>49</v>
       </c>
@@ -7393,7 +7393,7 @@
       <c r="I51" s="43"/>
       <c r="J51" s="43"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="45">
         <v>50</v>
       </c>
@@ -7417,7 +7417,7 @@
       <c r="I52" s="43"/>
       <c r="J52" s="43"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="45">
         <v>51</v>
       </c>
@@ -7433,7 +7433,7 @@
       <c r="I53" s="43"/>
       <c r="J53" s="43"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="45">
         <v>52</v>
       </c>
@@ -7449,7 +7449,7 @@
       <c r="I54" s="43"/>
       <c r="J54" s="43"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="45">
         <v>53</v>
       </c>
@@ -7465,7 +7465,7 @@
       <c r="I55" s="43"/>
       <c r="J55" s="43"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="45">
         <v>54</v>
       </c>
@@ -7481,7 +7481,7 @@
       <c r="I56" s="43"/>
       <c r="J56" s="43"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="45">
         <v>55</v>
       </c>
@@ -7497,7 +7497,7 @@
       <c r="I57" s="43"/>
       <c r="J57" s="43"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="45">
         <v>56</v>
       </c>
@@ -7513,7 +7513,7 @@
       <c r="I58" s="43"/>
       <c r="J58" s="43"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="45">
         <v>57</v>
       </c>
@@ -7529,7 +7529,7 @@
       <c r="I59" s="43"/>
       <c r="J59" s="43"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="45">
         <v>58</v>
       </c>
@@ -7545,7 +7545,7 @@
       <c r="I60" s="43"/>
       <c r="J60" s="43"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="45">
         <v>59</v>
       </c>
@@ -7561,7 +7561,7 @@
       <c r="I61" s="43"/>
       <c r="J61" s="43"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="45">
         <v>60</v>
       </c>
@@ -7577,7 +7577,7 @@
       <c r="I62" s="43"/>
       <c r="J62" s="43"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="45">
         <v>61</v>
       </c>
@@ -7593,7 +7593,7 @@
       <c r="I63" s="43"/>
       <c r="J63" s="43"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="45">
         <v>62</v>
       </c>
@@ -7609,7 +7609,7 @@
       <c r="I64" s="43"/>
       <c r="J64" s="43"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="45">
         <v>63</v>
       </c>
@@ -7625,7 +7625,7 @@
       <c r="I65" s="43"/>
       <c r="J65" s="43"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="45">
         <v>64</v>
       </c>
@@ -7641,7 +7641,7 @@
       <c r="I66" s="43"/>
       <c r="J66" s="43"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="45">
         <v>65</v>
       </c>
@@ -7657,7 +7657,7 @@
       <c r="I67" s="43"/>
       <c r="J67" s="43"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="45">
         <v>66</v>
       </c>
@@ -7681,7 +7681,7 @@
       <c r="I68" s="43"/>
       <c r="J68" s="43"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="45">
         <v>67</v>
       </c>
@@ -7707,7 +7707,7 @@
       <c r="I69" s="43"/>
       <c r="J69" s="43"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="45">
         <v>68</v>
       </c>
@@ -7744,15 +7744,15 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6999F5CC-A1A1-474D-BE11-DCCC063BE5A8}">
   <dimension ref="A1:N69"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="19.9765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.49609375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.49609375" customWidth="1"/>
-    <col min="14" max="14" width="11.9609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>497</v>
       </c>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="J1" s="46"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>1</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>2</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>3</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>4</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>5</v>
       </c>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N6" s="157"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>6</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>7</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>1.2718079999999998E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>8</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>5.0872319999999992E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>9</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>0.20348927999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>10</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>0.81395711999999987</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>11</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>3.2558284799999995</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>12</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>13.023313919999998</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>13</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>52.093255679999992</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>14</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>208.37302271999997</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>15</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>833.49209087999986</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>16</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>3333.9683635199995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>17</v>
       </c>
@@ -8346,7 +8346,7 @@
       <c r="I18" s="42"/>
       <c r="J18" s="42"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>18</v>
       </c>
@@ -8372,7 +8372,7 @@
       <c r="I19" s="42"/>
       <c r="J19" s="42"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>19</v>
       </c>
@@ -8398,7 +8398,7 @@
       <c r="I20" s="42"/>
       <c r="J20" s="42"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>20</v>
       </c>
@@ -8424,7 +8424,7 @@
       <c r="I21" s="42"/>
       <c r="J21" s="42"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>21</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="45">
         <v>23</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>24</v>
       </c>
@@ -8552,7 +8552,7 @@
       <c r="L25" s="53"/>
       <c r="M25" s="54"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>25</v>
       </c>
@@ -8578,7 +8578,7 @@
       <c r="I26" s="43"/>
       <c r="J26" s="43"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>26</v>
       </c>
@@ -8604,7 +8604,7 @@
       <c r="I27" s="43"/>
       <c r="J27" s="43"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>27</v>
       </c>
@@ -8630,7 +8630,7 @@
       <c r="I28" s="43"/>
       <c r="J28" s="43"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>28</v>
       </c>
@@ -8656,7 +8656,7 @@
       <c r="I29" s="43"/>
       <c r="J29" s="43"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>29</v>
       </c>
@@ -8682,7 +8682,7 @@
       <c r="I30" s="43"/>
       <c r="J30" s="43"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>30</v>
       </c>
@@ -8708,7 +8708,7 @@
       <c r="I31" s="43"/>
       <c r="J31" s="43"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>31</v>
       </c>
@@ -8734,7 +8734,7 @@
       <c r="I32" s="43"/>
       <c r="J32" s="43"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>32</v>
       </c>
@@ -8760,7 +8760,7 @@
       <c r="I33" s="43"/>
       <c r="J33" s="43"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>33</v>
       </c>
@@ -8786,7 +8786,7 @@
       <c r="I34" s="43"/>
       <c r="J34" s="43"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>34</v>
       </c>
@@ -8812,7 +8812,7 @@
       <c r="I35" s="43"/>
       <c r="J35" s="43"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>35</v>
       </c>
@@ -8838,7 +8838,7 @@
       <c r="I36" s="43"/>
       <c r="J36" s="43"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>36</v>
       </c>
@@ -8864,7 +8864,7 @@
       <c r="I37" s="43"/>
       <c r="J37" s="43"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>37</v>
       </c>
@@ -8890,7 +8890,7 @@
       <c r="I38" s="43"/>
       <c r="J38" s="43"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="45">
         <v>38</v>
       </c>
@@ -8916,7 +8916,7 @@
       <c r="I39" s="43"/>
       <c r="J39" s="43"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="45">
         <v>39</v>
       </c>
@@ -8942,7 +8942,7 @@
       <c r="I40" s="43"/>
       <c r="J40" s="43"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="45">
         <v>40</v>
       </c>
@@ -8970,7 +8970,7 @@
       <c r="I41" s="43"/>
       <c r="J41" s="43"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="45">
         <v>41</v>
       </c>
@@ -8996,7 +8996,7 @@
       <c r="I42" s="43"/>
       <c r="J42" s="43"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="45">
         <v>42</v>
       </c>
@@ -9022,7 +9022,7 @@
       <c r="I43" s="43"/>
       <c r="J43" s="43"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="45">
         <v>43</v>
       </c>
@@ -9048,7 +9048,7 @@
       <c r="I44" s="43"/>
       <c r="J44" s="43"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="45">
         <v>44</v>
       </c>
@@ -9074,7 +9074,7 @@
       <c r="I45" s="43"/>
       <c r="J45" s="43"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="45">
         <v>45</v>
       </c>
@@ -9100,7 +9100,7 @@
       <c r="I46" s="43"/>
       <c r="J46" s="43"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="45">
         <v>46</v>
       </c>
@@ -9126,7 +9126,7 @@
       <c r="I47" s="43"/>
       <c r="J47" s="43"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="45">
         <v>47</v>
       </c>
@@ -9152,7 +9152,7 @@
       <c r="I48" s="43"/>
       <c r="J48" s="43"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="45">
         <v>48</v>
       </c>
@@ -9178,7 +9178,7 @@
       <c r="I49" s="43"/>
       <c r="J49" s="43"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="45">
         <v>49</v>
       </c>
@@ -9204,7 +9204,7 @@
       <c r="I50" s="43"/>
       <c r="J50" s="43"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="45">
         <v>50</v>
       </c>
@@ -9230,7 +9230,7 @@
       <c r="I51" s="43"/>
       <c r="J51" s="43"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="45">
         <v>51</v>
       </c>
@@ -9256,7 +9256,7 @@
       <c r="I52" s="43"/>
       <c r="J52" s="43"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="45">
         <v>52</v>
       </c>
@@ -9282,7 +9282,7 @@
       <c r="I53" s="43"/>
       <c r="J53" s="43"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="45">
         <v>53</v>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="I54" s="43"/>
       <c r="J54" s="43"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="45">
         <v>54</v>
       </c>
@@ -9334,7 +9334,7 @@
       <c r="I55" s="43"/>
       <c r="J55" s="43"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="45">
         <v>55</v>
       </c>
@@ -9360,7 +9360,7 @@
       <c r="I56" s="43"/>
       <c r="J56" s="43"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="45">
         <v>56</v>
       </c>
@@ -9386,7 +9386,7 @@
       <c r="I57" s="43"/>
       <c r="J57" s="43"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="45">
         <v>57</v>
       </c>
@@ -9410,7 +9410,7 @@
       <c r="I58" s="43"/>
       <c r="J58" s="43"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="45">
         <v>58</v>
       </c>
@@ -9434,7 +9434,7 @@
       <c r="I59" s="43"/>
       <c r="J59" s="43"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="45">
         <v>59</v>
       </c>
@@ -9458,7 +9458,7 @@
       <c r="I60" s="43"/>
       <c r="J60" s="43"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="45">
         <v>60</v>
       </c>
@@ -9482,7 +9482,7 @@
       <c r="I61" s="43"/>
       <c r="J61" s="43"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="45">
         <v>61</v>
       </c>
@@ -9506,7 +9506,7 @@
       <c r="I62" s="43"/>
       <c r="J62" s="43"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="45">
         <v>62</v>
       </c>
@@ -9530,7 +9530,7 @@
       <c r="I63" s="43"/>
       <c r="J63" s="43"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="45">
         <v>63</v>
       </c>
@@ -9554,7 +9554,7 @@
       <c r="I64" s="43"/>
       <c r="J64" s="43"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="45">
         <v>64</v>
       </c>
@@ -9578,7 +9578,7 @@
       <c r="I65" s="43"/>
       <c r="J65" s="43"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="45">
         <v>65</v>
       </c>
@@ -9602,7 +9602,7 @@
       <c r="I66" s="43"/>
       <c r="J66" s="43"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="45">
         <v>66</v>
       </c>
@@ -9626,7 +9626,7 @@
       <c r="I67" s="43"/>
       <c r="J67" s="43"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="45">
         <v>67</v>
       </c>
@@ -9652,7 +9652,7 @@
       <c r="I68" s="43"/>
       <c r="J68" s="43"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="45">
         <v>68</v>
       </c>
@@ -9690,31 +9690,31 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{919EFAC6-4426-43D0-A745-0392D6158D41}">
   <dimension ref="A1:BC209"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.98828125" customWidth="1"/>
-    <col min="3" max="3" width="9.86328125" customWidth="1"/>
-    <col min="4" max="4" width="14.0546875" customWidth="1"/>
-    <col min="6" max="6" width="20.34375" customWidth="1"/>
-    <col min="7" max="7" width="37.36328125" customWidth="1"/>
-    <col min="9" max="9" width="5.30078125" customWidth="1"/>
-    <col min="10" max="10" width="10.48046875" customWidth="1"/>
-    <col min="11" max="11" width="11.34375" customWidth="1"/>
-    <col min="23" max="23" width="84.9609375" customWidth="1"/>
-    <col min="30" max="30" width="9.125" style="7" customWidth="1"/>
-    <col min="31" max="31" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.68359375" style="7" customWidth="1"/>
-    <col min="33" max="33" width="5.17578125" style="7" customWidth="1"/>
-    <col min="34" max="34" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="49" width="2.8359375" customWidth="1"/>
-    <col min="50" max="50" width="8.01171875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="5.671875" style="7" customWidth="1"/>
-    <col min="52" max="52" width="4.80859375" style="7" customWidth="1"/>
-    <col min="53" max="53" width="9.98828125" customWidth="1"/>
-    <col min="54" max="54" width="5.30078125" style="117" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="37.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="23" max="23" width="85" customWidth="1"/>
+    <col min="30" max="30" width="9.1640625" style="7" customWidth="1"/>
+    <col min="31" max="31" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.6640625" style="7" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="7" customWidth="1"/>
+    <col min="34" max="34" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="49" width="2.83203125" customWidth="1"/>
+    <col min="50" max="50" width="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="5.6640625" style="7" customWidth="1"/>
+    <col min="52" max="52" width="4.83203125" style="7" customWidth="1"/>
+    <col min="53" max="53" width="10" customWidth="1"/>
+    <col min="54" max="54" width="5.33203125" style="117" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
         <v>497</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -9859,7 +9859,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -9983,7 +9983,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -10466,7 +10466,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -10581,7 +10581,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -10650,7 +10650,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -10834,7 +10834,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="56" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="57" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="58" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="59" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -11098,7 +11098,7 @@
       <c r="F59" s="92"/>
       <c r="G59" s="94"/>
     </row>
-    <row r="60" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -11109,7 +11109,7 @@
       <c r="F60" s="92"/>
       <c r="G60" s="94"/>
     </row>
-    <row r="61" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -11119,7 +11119,7 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="62" spans="1:53" ht="21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:53" ht="22" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="63" spans="1:53" ht="21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:53" ht="22" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="64" spans="1:53" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:53" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -11307,8 +11307,8 @@
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
     </row>
-    <row r="69" spans="1:53" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:53" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB70" s="7" t="s">
         <v>720</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="71" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB71" s="7" t="s">
         <v>721</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="72" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB72" s="7" t="s">
         <v>721</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="73" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB73" s="7" t="s">
         <v>721</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="74" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB74" s="7" t="s">
         <v>722</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="75" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB75" s="7" t="s">
         <v>723</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="76" spans="1:53" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:53" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB76" s="7" t="s">
         <v>607</v>
       </c>
@@ -11417,7 +11417,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="77" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB77" s="7" t="s">
         <v>607</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="78" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB78" s="7" t="s">
         <v>736</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="79" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:53" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB79" s="7" t="s">
         <v>607</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="80" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:53" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB80" s="7" t="s">
         <v>607</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="81" spans="28:50" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="28:50" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB81" s="7" t="s">
         <v>723</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="82" spans="28:50" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="28:50" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB82" s="7" t="s">
         <v>722</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="83" spans="28:50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="28:50" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB83" s="7" t="s">
         <v>721</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="84" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB84" s="7" t="s">
         <v>721</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="85" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB85" s="7" t="s">
         <v>721</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="86" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AB86" s="7" t="s">
         <v>720</v>
       </c>
@@ -11553,8 +11553,8 @@
         <v>720</v>
       </c>
     </row>
-    <row r="87" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="28:50" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="28:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="28:50" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE91" s="97"/>
       <c r="AF91" s="124" t="s">
         <v>709</v>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="AU91" s="97"/>
     </row>
-    <row r="92" spans="28:50" x14ac:dyDescent="0.25">
+    <row r="92" spans="28:50" x14ac:dyDescent="0.2">
       <c r="AE92" s="7" t="s">
         <v>720</v>
       </c>
@@ -11656,12 +11656,12 @@
         <v>720</v>
       </c>
     </row>
-    <row r="112" spans="44:44" x14ac:dyDescent="0.25">
+    <row r="112" spans="44:44" x14ac:dyDescent="0.2">
       <c r="AR112" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="113" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="113" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AI113" t="s">
         <v>743</v>
       </c>
@@ -11687,7 +11687,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="114" spans="26:55" ht="21" x14ac:dyDescent="0.3">
+    <row r="114" spans="26:55" ht="22" x14ac:dyDescent="0.3">
       <c r="AF114" s="7" t="s">
         <v>741</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="115" spans="26:55" ht="21" x14ac:dyDescent="0.3">
+    <row r="115" spans="26:55" ht="22" x14ac:dyDescent="0.3">
       <c r="AE115" s="7" t="s">
         <v>720</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="116" spans="26:55" ht="59.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="26:55" ht="85" x14ac:dyDescent="0.2">
       <c r="AE116" s="97"/>
       <c r="AF116" s="124" t="s">
         <v>696</v>
@@ -11851,22 +11851,22 @@
         <v>726</v>
       </c>
     </row>
-    <row r="117" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="117" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AY117" s="121" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="118" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="118" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AY118" s="122" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="119" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="119" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AY119" s="123" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="122" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="122" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AB122" s="7" t="s">
         <v>720</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="123" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="123" spans="26:55" x14ac:dyDescent="0.2">
       <c r="Z123" t="s">
         <v>740</v>
       </c>
@@ -11911,7 +11911,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="124" spans="26:55" ht="59.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="26:55" ht="102" x14ac:dyDescent="0.2">
       <c r="Z124" t="s">
         <v>740</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="125" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="125" spans="26:55" x14ac:dyDescent="0.2">
       <c r="Z125" t="s">
         <v>740</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="126" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="126" spans="26:55" x14ac:dyDescent="0.2">
       <c r="Z126" t="s">
         <v>740</v>
       </c>
@@ -11998,7 +11998,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="127" spans="26:55" x14ac:dyDescent="0.25">
+    <row r="127" spans="26:55" x14ac:dyDescent="0.2">
       <c r="AA127" t="s">
         <v>739</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="128" spans="26:55" ht="59.25" x14ac:dyDescent="0.25">
+    <row r="128" spans="26:55" ht="85" x14ac:dyDescent="0.2">
       <c r="AA128" t="s">
         <v>739</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="129" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="129" spans="25:52" x14ac:dyDescent="0.2">
       <c r="AA129" t="s">
         <v>739</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="130" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="130" spans="25:52" x14ac:dyDescent="0.2">
       <c r="AA130" t="s">
         <v>739</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="131" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="131" spans="25:52" ht="17" x14ac:dyDescent="0.2">
       <c r="Z131" t="s">
         <v>740</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="132" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="132" spans="25:52" ht="17" x14ac:dyDescent="0.2">
       <c r="Z132" t="s">
         <v>740</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="133" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="133" spans="25:52" x14ac:dyDescent="0.2">
       <c r="AA133" t="s">
         <v>739</v>
       </c>
@@ -12147,7 +12147,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="134" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="134" spans="25:52" ht="17" x14ac:dyDescent="0.2">
       <c r="Z134" t="s">
         <v>740</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="135" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="135" spans="25:52" x14ac:dyDescent="0.2">
       <c r="Z135" t="s">
         <v>740</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="136" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="136" spans="25:52" x14ac:dyDescent="0.2">
       <c r="Z136" t="s">
         <v>740</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="137" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="137" spans="25:52" x14ac:dyDescent="0.2">
       <c r="Z137" t="s">
         <v>740</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="138" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="138" spans="25:52" x14ac:dyDescent="0.2">
       <c r="AB138" s="7" t="s">
         <v>720</v>
       </c>
@@ -12229,7 +12229,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="143" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="143" spans="25:52" ht="17" x14ac:dyDescent="0.2">
       <c r="Y143" s="102" t="s">
         <v>703</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="144" spans="25:52" x14ac:dyDescent="0.25">
+    <row r="144" spans="25:52" x14ac:dyDescent="0.2">
       <c r="AE144" s="7"/>
       <c r="AH144" s="7"/>
       <c r="AI144" s="7"/>
@@ -12257,7 +12257,7 @@
       <c r="AT144" s="7"/>
       <c r="AU144" s="7"/>
     </row>
-    <row r="146" spans="25:47" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="25:47" ht="68" x14ac:dyDescent="0.2">
       <c r="Z146" s="102" t="s">
         <v>706</v>
       </c>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="AU146" s="97"/>
     </row>
-    <row r="147" spans="25:47" x14ac:dyDescent="0.25">
+    <row r="147" spans="25:47" x14ac:dyDescent="0.2">
       <c r="Y147" s="102" t="s">
         <v>705</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="148" spans="25:47" x14ac:dyDescent="0.25">
+    <row r="148" spans="25:47" x14ac:dyDescent="0.2">
       <c r="AA148" s="99" t="s">
         <v>737</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="149" spans="25:47" x14ac:dyDescent="0.25">
+    <row r="149" spans="25:47" x14ac:dyDescent="0.2">
       <c r="AF149" s="7" t="s">
         <v>740</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="150" spans="25:47" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="25:47" ht="34" x14ac:dyDescent="0.2">
       <c r="Y150" s="99" t="s">
         <v>734</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="183" spans="29:55" ht="54.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="29:55" ht="55" x14ac:dyDescent="0.2">
       <c r="AI183" s="115" t="s">
         <v>746</v>
       </c>
@@ -12466,7 +12466,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="184" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI184" s="125" t="s">
         <v>739</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="185" spans="29:55" ht="54.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="29:55" ht="55" x14ac:dyDescent="0.2">
       <c r="AI185" s="115" t="s">
         <v>746</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="186" spans="29:55" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="29:55" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI186" s="125">
         <v>1</v>
       </c>
@@ -12607,7 +12607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="29:55" s="7" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="29:55" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI187" s="125" t="s">
         <v>721</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="188" spans="29:55" ht="48" x14ac:dyDescent="0.25">
+    <row r="188" spans="29:55" ht="49" x14ac:dyDescent="0.2">
       <c r="AI188" s="111" t="s">
         <v>696</v>
       </c>
@@ -12701,7 +12701,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="189" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="189" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC189" t="s">
         <v>746</v>
       </c>
@@ -12739,7 +12739,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="190" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="190" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC190" t="s">
         <v>746</v>
       </c>
@@ -12777,7 +12777,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="191" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="191" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC191" t="s">
         <v>746</v>
       </c>
@@ -12815,7 +12815,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="192" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="192" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC192" t="s">
         <v>746</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="193" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="193" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC193" t="s">
         <v>747</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="194" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="194" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC194" t="s">
         <v>749</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="195" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="195" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC195" t="s">
         <v>748</v>
       </c>
@@ -12967,7 +12967,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="196" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="196" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC196" t="s">
         <v>751</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="197" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="197" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC197" t="s">
         <v>749</v>
       </c>
@@ -13043,7 +13043,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="198" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="198" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC198" t="s">
         <v>749</v>
       </c>
@@ -13081,7 +13081,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="199" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="199" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC199" t="s">
         <v>747</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="200" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="200" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC200" t="s">
         <v>746</v>
       </c>
@@ -13149,7 +13149,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="201" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="201" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC201" t="s">
         <v>746</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="202" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="202" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC202" t="s">
         <v>746</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="203" spans="29:55" x14ac:dyDescent="0.25">
+    <row r="203" spans="29:55" x14ac:dyDescent="0.2">
       <c r="AC203" t="s">
         <v>746</v>
       </c>
@@ -13239,7 +13239,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="204" spans="29:55" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="29:55" ht="48" x14ac:dyDescent="0.2">
       <c r="AI204" s="111" t="s">
         <v>683</v>
       </c>
@@ -13276,7 +13276,7 @@
       <c r="AV204" s="111"/>
       <c r="AW204" s="111"/>
     </row>
-    <row r="205" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI205" s="125" t="s">
         <v>721</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="206" spans="29:55" s="7" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="29:55" s="7" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI206" s="125">
         <v>1</v>
       </c>
@@ -13370,7 +13370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="29:55" ht="54.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="29:55" ht="55" x14ac:dyDescent="0.2">
       <c r="AI207" s="115" t="s">
         <v>746</v>
       </c>
@@ -13407,7 +13407,7 @@
       <c r="AV207" s="115"/>
       <c r="AW207" s="115"/>
     </row>
-    <row r="208" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="29:55" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AI208" s="125" t="s">
         <v>739</v>
       </c>
@@ -13444,7 +13444,7 @@
       <c r="AV208" s="125"/>
       <c r="AW208" s="125"/>
     </row>
-    <row r="209" spans="35:49" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="209" spans="35:49" ht="48" x14ac:dyDescent="0.2">
       <c r="AI209" s="115" t="s">
         <v>746</v>
       </c>
@@ -13501,21 +13501,21 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4C112E-F624-3344-AA53-FFDF97BEB104}">
   <dimension ref="A1:Q70"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="19.9765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.37109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.9765625" customWidth="1"/>
-    <col min="10" max="10" width="18.49609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.00390625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5078125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="11.9609375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>497</v>
       </c>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>1</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>2</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>3</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>4</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>5</v>
       </c>
@@ -13701,7 +13701,7 @@
       <c r="P6" s="157"/>
       <c r="Q6" s="157"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>6</v>
       </c>
@@ -13736,7 +13736,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>7</v>
       </c>
@@ -13773,7 +13773,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>8</v>
       </c>
@@ -13810,7 +13810,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>9</v>
       </c>
@@ -13847,7 +13847,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>10</v>
       </c>
@@ -13884,7 +13884,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>11</v>
       </c>
@@ -13915,7 +13915,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>12</v>
       </c>
@@ -13946,7 +13946,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>13</v>
       </c>
@@ -13977,7 +13977,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>14</v>
       </c>
@@ -14008,7 +14008,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>15</v>
       </c>
@@ -14039,7 +14039,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>16</v>
       </c>
@@ -14070,7 +14070,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>17</v>
       </c>
@@ -14099,7 +14099,7 @@
       <c r="L18" s="42"/>
       <c r="M18" s="42"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>18</v>
       </c>
@@ -14128,7 +14128,7 @@
       <c r="L19" s="42"/>
       <c r="M19" s="42"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>19</v>
       </c>
@@ -14157,7 +14157,7 @@
       <c r="L20" s="42"/>
       <c r="M20" s="42"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>20</v>
       </c>
@@ -14186,7 +14186,7 @@
       <c r="L21" s="42"/>
       <c r="M21" s="42"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>21</v>
       </c>
@@ -14218,7 +14218,7 @@
       <c r="O22" s="48"/>
       <c r="P22" s="49"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -14249,7 +14249,7 @@
       <c r="N23" s="50"/>
       <c r="P23" s="51"/>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="44" t="s">
         <v>497</v>
       </c>
@@ -14280,7 +14280,7 @@
       <c r="N24" s="50"/>
       <c r="P24" s="51"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>23</v>
       </c>
@@ -14311,7 +14311,7 @@
       <c r="N25" s="50"/>
       <c r="P25" s="51"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>24</v>
       </c>
@@ -14331,7 +14331,7 @@
       <c r="O26" s="53"/>
       <c r="P26" s="54"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>25</v>
       </c>
@@ -14362,7 +14362,7 @@
       <c r="L27" s="43"/>
       <c r="M27" s="43"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>26</v>
       </c>
@@ -14393,7 +14393,7 @@
       <c r="L28" s="43"/>
       <c r="M28" s="43"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>27</v>
       </c>
@@ -14424,7 +14424,7 @@
       <c r="L29" s="43"/>
       <c r="M29" s="43"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>28</v>
       </c>
@@ -14455,7 +14455,7 @@
       <c r="L30" s="43"/>
       <c r="M30" s="43"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>29</v>
       </c>
@@ -14486,7 +14486,7 @@
       <c r="L31" s="43"/>
       <c r="M31" s="43"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>30</v>
       </c>
@@ -14517,7 +14517,7 @@
       <c r="L32" s="43"/>
       <c r="M32" s="43"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>31</v>
       </c>
@@ -14548,7 +14548,7 @@
       <c r="L33" s="43"/>
       <c r="M33" s="43"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>32</v>
       </c>
@@ -14579,7 +14579,7 @@
       <c r="L34" s="43"/>
       <c r="M34" s="43"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>33</v>
       </c>
@@ -14610,7 +14610,7 @@
       <c r="L35" s="43"/>
       <c r="M35" s="43"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>34</v>
       </c>
@@ -14641,7 +14641,7 @@
       <c r="L36" s="43"/>
       <c r="M36" s="43"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>35</v>
       </c>
@@ -14672,7 +14672,7 @@
       <c r="L37" s="43"/>
       <c r="M37" s="43"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>36</v>
       </c>
@@ -14703,7 +14703,7 @@
       <c r="L38" s="43"/>
       <c r="M38" s="43"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="45">
         <v>37</v>
       </c>
@@ -14734,7 +14734,7 @@
       <c r="L39" s="43"/>
       <c r="M39" s="43"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="45">
         <v>38</v>
       </c>
@@ -14765,7 +14765,7 @@
       <c r="L40" s="43"/>
       <c r="M40" s="43"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="45">
         <v>39</v>
       </c>
@@ -14796,7 +14796,7 @@
       <c r="L41" s="43"/>
       <c r="M41" s="43"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="45">
         <v>40</v>
       </c>
@@ -14827,7 +14827,7 @@
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="45">
         <v>41</v>
       </c>
@@ -14856,7 +14856,7 @@
       <c r="L43" s="43"/>
       <c r="M43" s="43"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="45">
         <v>42</v>
       </c>
@@ -14885,7 +14885,7 @@
       <c r="L44" s="43"/>
       <c r="M44" s="43"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="45">
         <v>43</v>
       </c>
@@ -14912,7 +14912,7 @@
       <c r="L45" s="43"/>
       <c r="M45" s="43"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="45">
         <v>44</v>
       </c>
@@ -14939,7 +14939,7 @@
       <c r="L46" s="43"/>
       <c r="M46" s="43"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="45">
         <v>45</v>
       </c>
@@ -14966,7 +14966,7 @@
       <c r="L47" s="43"/>
       <c r="M47" s="43"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="45">
         <v>46</v>
       </c>
@@ -14993,7 +14993,7 @@
       <c r="L48" s="43"/>
       <c r="M48" s="43"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="45">
         <v>47</v>
       </c>
@@ -15020,7 +15020,7 @@
       <c r="L49" s="43"/>
       <c r="M49" s="43"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="45">
         <v>48</v>
       </c>
@@ -15047,7 +15047,7 @@
       <c r="L50" s="43"/>
       <c r="M50" s="43"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="45">
         <v>49</v>
       </c>
@@ -15074,7 +15074,7 @@
       <c r="L51" s="43"/>
       <c r="M51" s="43"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="45">
         <v>50</v>
       </c>
@@ -15101,7 +15101,7 @@
       <c r="L52" s="43"/>
       <c r="M52" s="43"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="45">
         <v>51</v>
       </c>
@@ -15128,7 +15128,7 @@
       <c r="L53" s="43"/>
       <c r="M53" s="43"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="45">
         <v>52</v>
       </c>
@@ -15155,7 +15155,7 @@
       <c r="L54" s="43"/>
       <c r="M54" s="43"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="45">
         <v>53</v>
       </c>
@@ -15174,7 +15174,7 @@
       <c r="L55" s="43"/>
       <c r="M55" s="43"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="45">
         <v>54</v>
       </c>
@@ -15193,7 +15193,7 @@
       <c r="L56" s="43"/>
       <c r="M56" s="43"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="45">
         <v>55</v>
       </c>
@@ -15212,7 +15212,7 @@
       <c r="L57" s="43"/>
       <c r="M57" s="43"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="45">
         <v>56</v>
       </c>
@@ -15231,7 +15231,7 @@
       <c r="L58" s="43"/>
       <c r="M58" s="43"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="45">
         <v>57</v>
       </c>
@@ -15250,7 +15250,7 @@
       <c r="L59" s="43"/>
       <c r="M59" s="43"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="45">
         <v>58</v>
       </c>
@@ -15269,7 +15269,7 @@
       <c r="L60" s="43"/>
       <c r="M60" s="43"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="45">
         <v>59</v>
       </c>
@@ -15288,7 +15288,7 @@
       <c r="L61" s="43"/>
       <c r="M61" s="43"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="45">
         <v>60</v>
       </c>
@@ -15307,7 +15307,7 @@
       <c r="L62" s="43"/>
       <c r="M62" s="43"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="45">
         <v>61</v>
       </c>
@@ -15326,7 +15326,7 @@
       <c r="L63" s="43"/>
       <c r="M63" s="43"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="45">
         <v>62</v>
       </c>
@@ -15345,7 +15345,7 @@
       <c r="L64" s="43"/>
       <c r="M64" s="43"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="45">
         <v>63</v>
       </c>
@@ -15364,7 +15364,7 @@
       <c r="L65" s="43"/>
       <c r="M65" s="43"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="45">
         <v>64</v>
       </c>
@@ -15383,7 +15383,7 @@
       <c r="L66" s="43"/>
       <c r="M66" s="43"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="45">
         <v>65</v>
       </c>
@@ -15402,7 +15402,7 @@
       <c r="L67" s="43"/>
       <c r="M67" s="43"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="45">
         <v>66</v>
       </c>
@@ -15429,7 +15429,7 @@
       <c r="L68" s="43"/>
       <c r="M68" s="43"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="45">
         <v>67</v>
       </c>
@@ -15458,7 +15458,7 @@
       <c r="L69" s="43"/>
       <c r="M69" s="43"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="45">
         <v>68</v>
       </c>
@@ -15498,9 +15498,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622322C1-A87E-C54C-82D6-064DAB32880F}">
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr defaultColWidth="10.48046875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D1" s="137" t="s">
         <v>25</v>
       </c>
@@ -15519,7 +15519,7 @@
       <c r="Q1" s="137"/>
       <c r="R1" s="137"/>
     </row>
-    <row r="2" spans="1:26" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="74" t="s">
         <v>26</v>
       </c>
@@ -15599,7 +15599,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -15689,7 +15689,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -15869,7 +15869,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="74" t="s">
         <v>52</v>
       </c>
@@ -15883,7 +15883,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
         <v>4</v>
       </c>
@@ -15908,17 +15908,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DA3083-F993-FD4C-B84D-B0062B49C91E}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.55078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="5" width="14.55078125" customWidth="1"/>
-    <col min="6" max="6" width="13.4375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.48046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>56</v>
       </c>
@@ -15956,7 +15956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="K2" s="15"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -16016,7 +16016,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -16077,7 +16077,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -16106,7 +16106,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>91</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -16222,7 +16222,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>99</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -16280,7 +16280,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -16341,7 +16341,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>119</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>121</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>123</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -16524,7 +16524,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>135</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -16611,7 +16611,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -16669,7 +16669,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>143</v>
       </c>
@@ -16692,12 +16692,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84DC516-9730-9F4E-8850-3B18F1A65EF0}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -16717,7 +16717,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>154</v>
       </c>
@@ -16748,7 +16748,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>156</v>
       </c>
@@ -16776,7 +16776,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -16793,7 +16793,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>159</v>
       </c>
@@ -16810,7 +16810,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>162</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>163</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>164</v>
       </c>
@@ -16852,17 +16852,17 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="55" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>168</v>
       </c>
@@ -16878,13 +16878,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ED091F-F0A0-D14E-BA77-EAE6A7201215}">
   <dimension ref="A1:AK19"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="22" width="6.53515625" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="22" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>170</v>
       </c>
@@ -16997,7 +16997,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>171</v>
       </c>
@@ -17048,7 +17048,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
         <v>177</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>178</v>
       </c>
@@ -17234,7 +17234,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>187</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>188</v>
       </c>
@@ -17380,7 +17380,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
         <v>170</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
         <v>171</v>
       </c>
@@ -17462,7 +17462,7 @@
       <c r="P11" s="138"/>
       <c r="Q11" s="138"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
         <v>177</v>
       </c>
@@ -17515,7 +17515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>178</v>
       </c>
@@ -17550,7 +17550,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>187</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>188</v>
       </c>
@@ -17640,16 +17640,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C041953-8043-4B49-81E0-CAB4FDE7AD3D}">
   <dimension ref="A1:AL32"/>
-  <sheetFormatPr defaultColWidth="10.97265625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.49609375" customWidth="1"/>
-    <col min="3" max="17" width="6.53515625" customWidth="1"/>
-    <col min="18" max="18" width="14.0546875" customWidth="1"/>
-    <col min="19" max="23" width="6.53515625" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="17" width="6.5" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="23" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>170</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="2" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>171</v>
       </c>
@@ -17815,7 +17815,7 @@
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
         <v>177</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="139" t="s">
         <v>190</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="139"/>
       <c r="B5" s="4" t="s">
         <v>177</v>
@@ -18019,7 +18019,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="139"/>
       <c r="B6" s="4" t="s">
         <v>192</v>
@@ -18045,7 +18045,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="139"/>
       <c r="B7" s="4" t="s">
         <v>181</v>
@@ -18075,7 +18075,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="139" t="s">
         <v>193</v>
       </c>
@@ -18139,7 +18139,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="139"/>
       <c r="B9" s="4" t="s">
         <v>177</v>
@@ -18163,7 +18163,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="139"/>
       <c r="B10" s="4" t="s">
         <v>192</v>
@@ -18189,7 +18189,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="139"/>
       <c r="B11" s="4" t="s">
         <v>181</v>
@@ -18219,7 +18219,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="139" t="s">
         <v>188</v>
       </c>
@@ -18283,7 +18283,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="139"/>
       <c r="B13" s="4" t="s">
         <v>177</v>
@@ -18307,7 +18307,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="139"/>
       <c r="B14" s="4" t="s">
         <v>192</v>
@@ -18333,7 +18333,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="139"/>
       <c r="B15" s="4" t="s">
         <v>181</v>
@@ -18363,7 +18363,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>170</v>
       </c>
@@ -18429,7 +18429,7 @@
         <v>46631</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" s="23" t="s">
         <v>177</v>
       </c>
@@ -18497,7 +18497,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="139" t="s">
         <v>190</v>
       </c>
@@ -18543,7 +18543,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" s="139"/>
       <c r="B22" s="4" t="s">
         <v>192</v>
@@ -18557,7 +18557,7 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" s="139"/>
       <c r="B23" s="4" t="s">
         <v>195</v>
@@ -18571,13 +18571,13 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" s="139"/>
       <c r="B24" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" s="139" t="s">
         <v>193</v>
       </c>
@@ -18623,27 +18623,27 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" s="139"/>
       <c r="B26" s="4" t="s">
         <v>192</v>
       </c>
       <c r="J26" s="17"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" s="139"/>
       <c r="B27" s="4" t="s">
         <v>195</v>
       </c>
       <c r="J27" s="17"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" s="139"/>
       <c r="B28" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" s="139" t="s">
         <v>188</v>
       </c>
@@ -18689,13 +18689,13 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="139"/>
       <c r="B30" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="139"/>
       <c r="B31" s="4" t="s">
         <v>196</v>
@@ -18711,7 +18711,7 @@
       <c r="K31" s="34"/>
       <c r="L31" s="76"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="139"/>
       <c r="B32" s="4" t="s">
         <v>181</v>
@@ -18738,15 +18738,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29789358-47E8-40E4-B2F9-413684B6F778}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.015625" style="40" customWidth="1"/>
-    <col min="2" max="2" width="8.5078125" style="40"/>
-    <col min="3" max="3" width="10.97265625" style="40" customWidth="1"/>
-    <col min="4" max="16384" width="8.5078125" style="40"/>
+    <col min="1" max="1" width="17" style="40" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="40"/>
+    <col min="3" max="3" width="11" style="40" customWidth="1"/>
+    <col min="4" max="16384" width="8.5" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
         <v>198</v>
       </c>
@@ -18757,37 +18757,37 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="40" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="40" t="s">
         <v>205</v>
       </c>
@@ -18795,27 +18795,27 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="40" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="40" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
         <v>203</v>
       </c>
@@ -18823,27 +18823,27 @@
         <v>210</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="40" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="40" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="B21" s="40" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="B22" s="40" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>215</v>
       </c>
@@ -18851,7 +18851,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>217</v>
       </c>
@@ -18859,7 +18859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>218</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>219</v>
       </c>
@@ -18875,7 +18875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>220</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="40" t="s">
         <v>203</v>
       </c>
@@ -18891,7 +18891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>208</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>221</v>
       </c>
@@ -18915,7 +18915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>222</v>
       </c>
@@ -18923,7 +18923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>204</v>
       </c>
@@ -18939,17 +18939,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B565E103-35D6-4849-8F8F-BBFE728E8F6B}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="72.5078125" style="58" customWidth="1"/>
-    <col min="2" max="2" width="34.03125" style="58" customWidth="1"/>
-    <col min="3" max="3" width="38.47265625" style="58" customWidth="1"/>
-    <col min="4" max="4" width="24.04296875" style="58" customWidth="1"/>
-    <col min="5" max="5" width="22.93359375" style="58" customWidth="1"/>
-    <col min="6" max="6" width="28.484375" style="58" customWidth="1"/>
-    <col min="7" max="7" width="11.9609375" style="58" customWidth="1"/>
-    <col min="8" max="8" width="23.55078125" style="58" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.5078125" style="58"/>
+    <col min="1" max="1" width="72.5" style="58" customWidth="1"/>
+    <col min="2" max="2" width="34" style="58" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="58" customWidth="1"/>
+    <col min="4" max="4" width="24" style="58" customWidth="1"/>
+    <col min="5" max="5" width="23" style="58" customWidth="1"/>
+    <col min="6" max="6" width="28.5" style="58" customWidth="1"/>
+    <col min="7" max="7" width="12" style="58" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="58" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.5" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -19524,12 +19524,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B5B836-10D3-1D4A-8D7C-1BB126EFB3F2}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.94921875" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>285</v>
       </c>
@@ -19540,62 +19540,62 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>291</v>
       </c>
@@ -19603,22 +19603,22 @@
         <v>292</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="40" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>215</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>217</v>
       </c>
@@ -19634,7 +19634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>218</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>219</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>220</v>
       </c>
@@ -19658,7 +19658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>291</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>208</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>97</v>
       </c>
@@ -19682,7 +19682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>221</v>
       </c>
@@ -19690,7 +19690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>222</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>204</v>
       </c>
@@ -19706,7 +19706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>294</v>
       </c>
@@ -19714,12 +19714,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>99</v>
       </c>
@@ -19727,17 +19727,17 @@
         <v>296</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>299</v>
       </c>
@@ -19745,17 +19745,17 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -19763,12 +19763,12 @@
         <v>303</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>305</v>
       </c>
@@ -19779,11 +19779,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D79752651F8804F853F70D8EFCD890F" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23eae337d8896d6afe097a837b9dc0d1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="34ba8e32-dead-459b-a837-1ef289c0b6d1" xmlns:ns3="9f47adc2-9a42-47a5-94d8-1ff815753c27" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aab01ed21353a89acdf6e3a5f8ee2dda" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="34ba8e32-dead-459b-a837-1ef289c0b6d1"/>
-    <xsd:import namespace="9f47adc2-9a42-47a5-94d8-1ff815753c27"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="61dcf3c9-eb15-454e-81ca-9882d19829ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c2ce6744-4b49-4235-bf64-039aa398445e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010009F1B3491505B544ABCF4DBFD995A328" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="86b8ba780bd6e9be5664127850d8b7b9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c2ce6744-4b49-4235-bf64-039aa398445e" xmlns:ns3="61dcf3c9-eb15-454e-81ca-9882d19829ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cd7fef6318788f8bc60e4eef8ec9355d" ns2:_="" ns3:_="">
+    <xsd:import namespace="c2ce6744-4b49-4235-bf64-039aa398445e"/>
+    <xsd:import namespace="61dcf3c9-eb15-454e-81ca-9882d19829ae"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -19802,11 +19821,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -19814,21 +19829,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="25" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="34ba8e32-dead-459b-a837-1ef289c0b6d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c2ce6744-4b49-4235-bf64-039aa398445e" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -19880,23 +19881,13 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9f47adc2-9a42-47a5-94d8-1ff815753c27" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="61dcf3c9-eb15-454e-81ca-9882d19829ae" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -19925,7 +19916,7 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{9b6b7b6e-5c4a-4092-9da6-7c71c9c5fc7c}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9f47adc2-9a42-47a5-94d8-1ff815753c27">
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{1ae93f37-7ef2-4de8-a45f-21fc26b842fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="61dcf3c9-eb15-454e-81ca-9882d19829ae">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -20036,30 +20027,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9f47adc2-9a42-47a5-94d8-1ff815753c27" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34ba8e32-dead-459b-a837-1ef289c0b6d1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287B89D6-A6B4-4ABD-80E5-EC264652345C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3262A83-6CA8-4E6D-99F6-560E11F0EAD2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20076,9 +20049,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3262A83-6CA8-4E6D-99F6-560E11F0EAD2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6CEEDFB-11A0-48FA-950C-ED0EA9155890}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="c2ce6744-4b49-4235-bf64-039aa398445e"/>
+    <ds:schemaRef ds:uri="61dcf3c9-eb15-454e-81ca-9882d19829ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>